--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP_R12_MonitorizarRestriccionesOrigen\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C16D3B0-C2BD-4BAA-BE9F-245948F0E032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6EFFF8-2E75-4129-BAA5-CF10C4CE3A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="84">
   <si>
     <t>Name</t>
   </si>
@@ -281,17 +281,33 @@
   </si>
   <si>
     <t>Playout</t>
+  </si>
+  <si>
+    <t>MonitorizarRestriccionesReporte_{0}.xlsx</t>
+  </si>
+  <si>
+    <t>Nombre del reporte descargado desde SAP con formato de fecha añomesdia (yyyyMMdd)</t>
+  </si>
+  <si>
+    <t>ReportName</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -374,12 +390,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -394,20 +416,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -743,7 +768,17 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3006,10 +3041,10 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="15" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
@@ -3020,10 +3055,10 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="15" t="s">
         <v>67</v>
       </c>
       <c r="C7" s="9" t="s">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP_R12_MonitorizarRestriccionesOrigen\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6EFFF8-2E75-4129-BAA5-CF10C4CE3A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366F712C-70C9-4F3B-B48D-11FBFA3E427F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="81">
   <si>
     <t>Name</t>
   </si>
@@ -214,42 +214,12 @@
     <t>La ruta del ejecutor de SAP Logon</t>
   </si>
   <si>
-    <t>InitialInpuPath</t>
-  </si>
-  <si>
-    <t>Ruta del insumo inicial incluido el nombre del archivo</t>
-  </si>
-  <si>
-    <t>ISR_InitialInpuPath</t>
-  </si>
-  <si>
-    <t>FinalReportName</t>
-  </si>
-  <si>
-    <t>Nombre del reporte final</t>
-  </si>
-  <si>
-    <t>SEGUIMIENTO REPUESTOS {0}.xlsm</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
-    <t>SAP_SheetName</t>
-  </si>
-  <si>
     <t>Nombre de la hoja del reportes SAP</t>
   </si>
   <si>
-    <t>ISR_FinalFolderReportPath</t>
-  </si>
-  <si>
-    <t>Ruta de la carpeta para guardar el reporte final</t>
-  </si>
-  <si>
-    <t>FinalFolderReportPath</t>
-  </si>
-  <si>
     <t>AMP_R12_MonitorizarRestriccionesOrigen</t>
   </si>
   <si>
@@ -290,24 +260,38 @@
   </si>
   <si>
     <t>ReportName</t>
+  </si>
+  <si>
+    <t>ReportPath</t>
+  </si>
+  <si>
+    <t>Ruta para almacenar el reporte</t>
+  </si>
+  <si>
+    <t>MRO_ReportPath</t>
+  </si>
+  <si>
+    <t>ReportSheetName</t>
+  </si>
+  <si>
+    <t>SAP_MROTransactionDifference</t>
+  </si>
+  <si>
+    <t>Transacción para ejecutar en SAP posiciones diferentes</t>
+  </si>
+  <si>
+    <t>MROTransactionDifference</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -390,18 +374,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -416,23 +394,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z992"/>
+  <dimension ref="A1:Z991"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -718,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -729,7 +705,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>55</v>
@@ -747,37 +723,29 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>61</v>
+      <c r="A7" s="13" t="s">
+        <v>77</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>64</v>
+      <c r="A8" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="A9" s="13"/>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -981,7 +949,7 @@
     <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1761,7 +1729,6 @@
     <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2949,165 +2916,165 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="A6" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>59</v>
+      <c r="D6" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="A7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>68</v>
+      <c r="D7" s="10" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="A8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>74</v>
+      <c r="D8" s="13" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="A9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>76</v>
+      <c r="D9" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="A10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>79</v>
+      <c r="D10" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP_R12_MonitorizarRestriccionesOrigen\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366F712C-70C9-4F3B-B48D-11FBFA3E427F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D609A2E-C9A0-44B7-8A4B-7D9CCEA2F2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="90">
   <si>
     <t>Name</t>
   </si>
@@ -253,9 +253,6 @@
     <t>Playout</t>
   </si>
   <si>
-    <t>MonitorizarRestriccionesReporte_{0}.xlsx</t>
-  </si>
-  <si>
     <t>Nombre del reporte descargado desde SAP con formato de fecha añomesdia (yyyyMMdd)</t>
   </si>
   <si>
@@ -281,17 +278,54 @@
   </si>
   <si>
     <t>MROTransactionDifference</t>
+  </si>
+  <si>
+    <t>MRO_EmailTo</t>
+  </si>
+  <si>
+    <t>cuentas de email de destinatarios de notificación</t>
+  </si>
+  <si>
+    <t>SmtpEmailserver</t>
+  </si>
+  <si>
+    <t>smtp.office365.com</t>
+  </si>
+  <si>
+    <t>SmtpPort</t>
+  </si>
+  <si>
+    <t>puerto para notificación de email por SMTP</t>
+  </si>
+  <si>
+    <t>servidor para notificación de email por SMTP</t>
+  </si>
+  <si>
+    <t>PosiSoftEmailSender</t>
+  </si>
+  <si>
+    <t>Email accout to notify</t>
+  </si>
+  <si>
+    <t>Reporte_{0}.xlsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -396,18 +430,18 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -723,8 +757,8 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>77</v>
+      <c r="A7" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>58</v>
@@ -734,21 +768,49 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11">
+        <v>587</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+    </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3008,17 +3070,17 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>76</v>
+      <c r="A6" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>75</v>
+      <c r="D6" s="11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3036,21 +3098,21 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>78</v>
+      <c r="A8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>79</v>
+      <c r="D8" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="13" t="s">
         <v>67</v>
       </c>
       <c r="B9" s="10" t="s">
@@ -3077,7 +3139,20 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP_R12_MonitorizarRestriccionesOrigen\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D609A2E-C9A0-44B7-8A4B-7D9CCEA2F2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50122175-F357-409D-A074-D5B406F125EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -250,9 +250,6 @@
     <t>layout para generar el reporte en SAP</t>
   </si>
   <si>
-    <t>Playout</t>
-  </si>
-  <si>
     <t>Nombre del reporte descargado desde SAP con formato de fecha añomesdia (yyyyMMdd)</t>
   </si>
   <si>
@@ -308,17 +305,27 @@
   </si>
   <si>
     <t>Reporte_{0}.xlsx</t>
+  </si>
+  <si>
+    <t>SAPLayout</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -428,17 +435,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -758,7 +766,7 @@
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>58</v>
@@ -769,46 +777,46 @@
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
         <v>87</v>
-      </c>
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
         <v>82</v>
       </c>
-      <c r="B10" t="s">
-        <v>83</v>
-      </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11">
         <v>587</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3071,16 +3079,16 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3099,16 +3107,16 @@
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3126,8 +3134,8 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>70</v>
+      <c r="A10" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>68</v>
@@ -3141,16 +3149,16 @@
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
